--- a/Starfront/文档/配置表/__tables__.xlsx
+++ b/Starfront/文档/配置表/__tables__.xlsx
@@ -1512,17 +1512,17 @@
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <ns0:cols>
-    <ns0:col min="1" max="1" width="6.625" customWidth="1"/>
-    <ns0:col min="2" max="2" width="30.25" customWidth="1"/>
-    <ns0:col min="3" max="3" width="38.25" customWidth="1"/>
-    <ns0:col min="4" max="4" width="56.125" customWidth="1"/>
-    <ns0:col min="5" max="5" width="33.125" customWidth="1"/>
-    <ns0:col min="6" max="6" width="95.75" customWidth="1"/>
-    <ns0:col min="7" max="7" width="33.875" customWidth="1"/>
-    <ns0:col min="8" max="8" width="58.625" customWidth="1"/>
-    <ns0:col min="9" max="9" width="19.125" customWidth="1"/>
-    <ns0:col min="10" max="10" width="5.25" customWidth="1"/>
-    <ns0:col min="11" max="11" width="36.5" customWidth="1"/>
+    <ns0:col min="1" max="1" width="12" customWidth="1"/>
+    <ns0:col min="2" max="2" width="32" customWidth="1"/>
+    <ns0:col min="3" max="3" width="39" customWidth="1"/>
+    <ns0:col min="4" max="4" width="58" customWidth="1"/>
+    <ns0:col min="5" max="5" width="35" customWidth="1"/>
+    <ns0:col min="6" max="6" width="64" customWidth="1"/>
+    <ns0:col min="7" max="7" width="35" customWidth="1"/>
+    <ns0:col min="8" max="8" width="62" customWidth="1"/>
+    <ns0:col min="9" max="9" width="18" customWidth="1"/>
+    <ns0:col min="10" max="10" width="12" customWidth="1"/>
+    <ns0:col min="11" max="11" width="35" customWidth="1"/>
   </ns0:cols>
   <ns0:sheetData>
     <ns0:row r="1" s="1" customFormat="1" ht="16.5">
@@ -2040,7 +2040,110 @@
       <ns0:c r="J19" s="102"/>
       <ns0:c r="K19" s="103"/>
     </ns0:row>
+    <ns0:row r="20" ht="24" customHeight="1">
+      <ns0:c r="A20" s="93"/>
+      <ns0:c r="B20" t="str" s="94">
+        <ns0:v>cfgObj.SkillObj</ns0:v>
+      </ns0:c>
+      <ns0:c r="C20" t="str" s="95">
+        <ns0:v>resource.SkillResource</ns0:v>
+      </ns0:c>
+      <ns0:c r="D20" s="96" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" t="str" s="97">
+        <ns0:v>SkillResource.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F20" t="str" s="98">
+        <ns0:v>id</ns0:v>
+      </ns0:c>
+      <ns0:c r="G20" t="str" s="99">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H20" s="100"/>
+      <ns0:c r="I20" t="str" s="101">
+        <ns0:v>技能表</ns0:v>
+      </ns0:c>
+      <ns0:c r="J20" s="102"/>
+      <ns0:c r="K20" s="103"/>
+    </ns0:row>
+    <ns0:row r="21" ht="24" customHeight="1">
+      <ns0:c r="B21" t="str" s="94">
+        <ns0:v>cfgObj.ProjectileObj</ns0:v>
+      </ns0:c>
+      <ns0:c r="C21" t="str" s="95">
+        <ns0:v>resource.ProjectileResource</ns0:v>
+      </ns0:c>
+      <ns0:c r="D21" s="96" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" t="str" s="97">
+        <ns0:v>ProjectileResource.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F21" t="str" s="98">
+        <ns0:v>id</ns0:v>
+      </ns0:c>
+      <ns0:c r="G21" t="str" s="99">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="I21" t="str" s="101">
+        <ns0:v>弹道表</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22" ht="24" customHeight="1">
+      <ns0:c r="A22" s="0"/>
+      <ns0:c r="B22" t="str" s="94">
+        <ns0:v>cfgObj.BattleAIProfileObj</ns0:v>
+      </ns0:c>
+      <ns0:c r="C22" t="str" s="95">
+        <ns0:v>resource.BattleAIProfileResource</ns0:v>
+      </ns0:c>
+      <ns0:c r="D22" s="96" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" t="str" s="97">
+        <ns0:v>BattleAIProfileResource.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F22" t="str" s="98">
+        <ns0:v>id</ns0:v>
+      </ns0:c>
+      <ns0:c r="G22" t="str" s="99">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H22" s="0"/>
+      <ns0:c r="I22" t="str" s="101">
+        <ns0:v>电脑玩家发展策略</ns0:v>
+      </ns0:c>
+      <ns0:c r="J22" s="0"/>
+      <ns0:c r="K22" s="0"/>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="B23" t="str" s="94">
+        <ns0:v>cfgObj.UnitVisualObj</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" t="str" s="95">
+        <ns0:v>resource.UnitVisualResource</ns0:v>
+      </ns0:c>
+      <ns0:c r="D23" s="96" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" t="str" s="97">
+        <ns0:v>UnitVisualResource.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F23" t="str" s="98">
+        <ns0:v>id</ns0:v>
+      </ns0:c>
+      <ns0:c r="G23" t="str" s="99">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="I23" t="str" s="101">
+        <ns0:v>单位共用形象参数</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:dimension ref="A1:K23"/>
+  <ns0:mergeCells count="0"/>
+  <ns0:dataValidations count="0"/>
 </ns0:worksheet>
 </file>